--- a/artfynd/A 23991-2022 artfynd.xlsx
+++ b/artfynd/A 23991-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23991-2022 artfynd.xlsx
+++ b/artfynd/A 23991-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2635,6 +2635,556 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120595540</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Glasbruksvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>431895</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7050597</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120595531</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Glasbruksvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>431909</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7050574</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120595527</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Glasbruksvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>431957</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7050532</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120595568</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Glasbruksvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>431885</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7050687</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120595549</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Glasbruksvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>431924</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7050569</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
